--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_15_R2.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_15_R2.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>J. DOWTIN JR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8717</v>
+        <v>2.3087</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5587</v>
+        <v>2.9679</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.6592</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8446</v>
+        <v>1.1199</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.4069</v>
+        <v>-3.1596</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5622</v>
+        <v>4.2796</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.219</v>
+        <v>3.1359</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3662</v>
+        <v>-1.4145</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1472</v>
+        <v>4.5504</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6256</v>
+        <v>-2.016</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0406</v>
+        <v>-1.7452</v>
       </c>
       <c r="O2" t="n">
-        <v>0.415</v>
+        <v>-0.2708</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0876</v>
+        <v>3.0154</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0876</v>
+        <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1649</v>
+        <v>-0.8962</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5637</v>
+        <v>-0.4516</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3989</v>
+        <v>-0.4446</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5361</v>
+        <v>-0.9304</v>
       </c>
       <c r="W2" t="n">
-        <v>1.214</v>
+        <v>0.2836</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7501</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5001</v>
+        <v>1.4721</v>
       </c>
       <c r="E3" t="n">
-        <v>2.178</v>
+        <v>1.1164</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3221</v>
+        <v>0.3557</v>
       </c>
       <c r="G3" t="n">
         <v>-1.0075</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1312</v>
+        <v>0.1032</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7695</v>
+        <v>0.7079</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6383</v>
+        <v>-0.6047</v>
       </c>
       <c r="V3" t="n">
         <v>2.1444</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. DOWTIN JR</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0215</v>
+        <v>1.3891</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9496</v>
+        <v>2.1433</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.928</v>
+        <v>-0.7542</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1199</v>
+        <v>-0.8446</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.1596</v>
+        <v>-1.4069</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2796</v>
+        <v>0.5622</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1359</v>
+        <v>-0.219</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.4145</v>
+        <v>-0.3662</v>
       </c>
       <c r="L4" t="n">
-        <v>4.5504</v>
+        <v>0.1472</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.016</v>
+        <v>-0.6256</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7452</v>
+        <v>-1.0406</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2708</v>
+        <v>0.415</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0154</v>
+        <v>2.0876</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0154</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.1833</v>
+        <v>0.6822</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4699</v>
+        <v>1.1483</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7134</v>
+        <v>-0.4661</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9304</v>
+        <v>-0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2836</v>
+        <v>1.214</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.214</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. LEAF</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4658</v>
+        <v>0.5971</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0758</v>
+        <v>-0.2289</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5416</v>
+        <v>0.826</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.278</v>
+        <v>1.1844</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4889</v>
+        <v>-1.5258</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2109</v>
+        <v>2.7101</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6621</v>
+        <v>2.0639</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5517</v>
+        <v>-0.1275</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1104</v>
+        <v>2.1913</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9401</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0406</v>
+        <v>-1.3983</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1005</v>
+        <v>0.5188</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5515</v>
+        <v>3.2473</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9241</v>
+        <v>-0.9247</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8521</v>
+        <v>-0.7387</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0721</v>
+        <v>-0.186</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2525</v>
+        <v>-1.7501</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1107</v>
+        <v>-0.3943</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2004</v>
+        <v>0.5782</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0755</v>
+        <v>0.3861</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1249</v>
+        <v>0.1921</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1569</v>
@@ -922,13 +922,13 @@
         <v>2.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0912</v>
+        <v>-0.7134</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6168</v>
+        <v>-0.3062</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4744</v>
+        <v>-0.4072</v>
       </c>
       <c r="V6" t="n">
         <v>2.1444</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2166</v>
+        <v>-0.2338</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5415</v>
+        <v>-0.6595</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3249</v>
+        <v>0.4257</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7477</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6286</v>
+        <v>-0.6458</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3383</v>
+        <v>0.2203</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9669</v>
+        <v>-0.8661</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>T. LEAF</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3026</v>
+        <v>-0.7467</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8933</v>
+        <v>-2.0194</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5907</v>
+        <v>1.2727</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1844</v>
+        <v>-0.278</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5258</v>
+        <v>-0.4889</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7101</v>
+        <v>0.2109</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0639</v>
+        <v>0.6621</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1275</v>
+        <v>0.5517</v>
       </c>
       <c r="L9" t="n">
-        <v>2.1913</v>
+        <v>0.1104</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.9401</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3983</v>
+        <v>-1.0406</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5188</v>
+        <v>0.1005</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0876</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R9" t="n">
-        <v>3.2473</v>
+        <v>2.5515</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8244</v>
+        <v>0.7117</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4031</v>
+        <v>0.9085</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4213</v>
+        <v>-0.1968</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.7501</v>
+        <v>-0.2525</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3943</v>
+        <v>-0.1107</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3558</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.395</v>
+        <v>-3.7629</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8079</v>
+        <v>-1.6717</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5871</v>
+        <v>-2.0912</v>
       </c>
       <c r="G10" t="n">
         <v>-4.3211</v>
@@ -1234,13 +1234,13 @@
         <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1461</v>
+        <v>-0.514</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4778</v>
+        <v>-0.3416</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3317</v>
+        <v>-0.1724</v>
       </c>
       <c r="V10" t="n">
         <v>1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9555</v>
+        <v>-3.8775</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.31</v>
+        <v>-2.3664</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6455</v>
+        <v>-1.5111</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4884</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7739</v>
+        <v>-0.6959</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5149</v>
+        <v>0.4288</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.259</v>
+        <v>-1.1246</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1418</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.442</v>
+        <v>-7.6033</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5072</v>
+        <v>-5.6684</v>
       </c>
       <c r="F12" t="n">
         <v>-1.9349</v>
@@ -1390,10 +1390,10 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2344</v>
+        <v>-1.3957</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3339</v>
+        <v>-0.4951</v>
       </c>
       <c r="U12" t="n">
         <v>-0.9006</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.4239</v>
+        <v>-10.0507</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.2651</v>
+        <v>-4.891799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.1588</v>
+        <v>-5.1589</v>
       </c>
       <c r="G13" t="n">
         <v>-6.919200000000001</v>
@@ -1441,10 +1441,10 @@
         <v>8.3985</v>
       </c>
       <c r="J13" t="n">
-        <v>3.340600000000001</v>
+        <v>3.3406</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.801700000000001</v>
+        <v>-3.8017</v>
       </c>
       <c r="L13" t="n">
         <v>7.1424</v>
@@ -1468,13 +1468,13 @@
         <v>20.87580000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.8937</v>
+        <v>-4.5206</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6324999999999998</v>
+        <v>1.0059</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.526299999999999</v>
+        <v>-5.5264</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9304</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2869</v>
+        <v>5.8316</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5968</v>
+        <v>3.9507</v>
       </c>
       <c r="F14" t="n">
-        <v>1.69</v>
+        <v>1.8809</v>
       </c>
       <c r="G14" t="n">
         <v>2.9866</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2333</v>
+        <v>0.3115</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0395</v>
+        <v>0.3934</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2728</v>
+        <v>-0.0819</v>
       </c>
       <c r="V14" t="n">
         <v>0.6778999999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9342</v>
+        <v>4.3589</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9422</v>
+        <v>0.1715</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.008</v>
+        <v>4.1874</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7779</v>
+        <v>2.6511</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4465</v>
+        <v>1.4633</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3314</v>
+        <v>1.1878</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8499</v>
+        <v>1.0713</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9361</v>
+        <v>0.8773</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9139</v>
+        <v>0.1939</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.072</v>
+        <v>1.5798</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5105</v>
+        <v>0.586</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5825</v>
+        <v>0.9939</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>3.695</v>
+        <v>0.0815</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1102</v>
+        <v>0.1182</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5847</v>
+        <v>-0.0367</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.0026</v>
+        <v>0.9304</v>
       </c>
       <c r="W15" t="n">
         <v>0.1418</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1444</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3702</v>
+        <v>3.2435</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5362</v>
+        <v>3.0621</v>
       </c>
       <c r="F16" t="n">
-        <v>3.9064</v>
+        <v>0.1815</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6511</v>
+        <v>1.299</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4633</v>
+        <v>2.6206</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1878</v>
+        <v>-1.3216</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0713</v>
+        <v>2.0744</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8773</v>
+        <v>2.2351</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1939</v>
+        <v>-0.1607</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5798</v>
+        <v>-0.7754</v>
       </c>
       <c r="N16" t="n">
-        <v>0.586</v>
+        <v>0.3856</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9939</v>
+        <v>-1.1609</v>
       </c>
       <c r="P16" t="n">
         <v>0.6959</v>
@@ -1702,28 +1702,28 @@
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9071</v>
+        <v>0.7125</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5895</v>
+        <v>0.3973</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3176</v>
+        <v>0.3152</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9304</v>
+        <v>0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>1.7501</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7886</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.168</v>
+        <v>2.5885</v>
       </c>
       <c r="E17" t="n">
-        <v>2.343</v>
+        <v>4.055</v>
       </c>
       <c r="F17" t="n">
-        <v>0.825</v>
+        <v>-1.4664</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9243</v>
+        <v>2.7779</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4094</v>
+        <v>2.4465</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4851</v>
+        <v>0.3314</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9707</v>
+        <v>3.8499</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8234</v>
+        <v>1.9361</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1472</v>
+        <v>1.9139</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0464</v>
+        <v>-1.072</v>
       </c>
       <c r="N17" t="n">
-        <v>0.586</v>
+        <v>0.5105</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6323</v>
+        <v>-1.5825</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>2.298</v>
+        <v>1.3493</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3724</v>
+        <v>1.223</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9256</v>
+        <v>0.1263</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.214</v>
+        <v>-2.0026</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.214</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1712</v>
+        <v>2.0564</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4723</v>
+        <v>1.3994</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3011</v>
+        <v>0.657</v>
       </c>
       <c r="G18" t="n">
-        <v>1.299</v>
+        <v>0.9243</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6206</v>
+        <v>1.4094</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3216</v>
+        <v>-0.4851</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0744</v>
+        <v>0.9707</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2351</v>
+        <v>0.8234</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1607</v>
+        <v>0.1472</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7754</v>
+        <v>-0.0464</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3856</v>
+        <v>0.586</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1609</v>
+        <v>-0.6323</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3598</v>
+        <v>1.1863</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1924</v>
+        <v>0.4288</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1674</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5361</v>
+        <v>-1.214</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>-1.214</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8933</v>
+        <v>1.4608</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4206</v>
+        <v>-0.1692</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4727</v>
+        <v>1.63</v>
       </c>
       <c r="G19" t="n">
         <v>1.4193</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.4874</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9006</v>
+        <v>0.3108</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0193</v>
+        <v>0.1766</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6778999999999999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.826</v>
+        <v>0.663</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1654</v>
+        <v>0.0254</v>
       </c>
       <c r="G20" t="n">
         <v>1.0923</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.4806</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7196</v>
+        <v>0.3657</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.076</v>
+        <v>0.1149</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6778999999999999</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6605</v>
+        <v>-0.2675</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6725</v>
+        <v>-2.4357</v>
       </c>
       <c r="F21" t="n">
-        <v>1.012</v>
+        <v>2.1682</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3438</v>
+        <v>0.5304</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3957</v>
+        <v>1.6951</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7395</v>
+        <v>-1.1647</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4603</v>
+        <v>0.6875</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3031</v>
+        <v>1.163</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1571</v>
+        <v>-0.4756</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.804</v>
+        <v>-0.1571</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0926</v>
+        <v>0.5321</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8966</v>
+        <v>-0.6891</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8556</v>
+        <v>-3.7112</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-5.7988</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>0.861</v>
+        <v>0.2328</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6686</v>
+        <v>0.3894</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1924</v>
+        <v>-0.1566</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.6805</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.2862</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5138</v>
+        <v>-0.7391</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7229</v>
+        <v>-1.9084</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7909</v>
+        <v>1.1693</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5532</v>
+        <v>-0.3438</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.3957</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4885</v>
+        <v>-0.7395</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5815</v>
+        <v>0.4603</v>
       </c>
       <c r="K22" t="n">
-        <v>0.168</v>
+        <v>0.3031</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.1571</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0283</v>
+        <v>-0.804</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2327</v>
+        <v>0.0926</v>
       </c>
       <c r="O22" t="n">
-        <v>0.261</v>
+        <v>-0.8966</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q22" t="n">
+        <v>-3.4793</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.6237</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.7824</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.6778999999999999</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.6778999999999999</v>
+      </c>
+      <c r="X22" t="n">
         <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.4639</v>
-      </c>
-      <c r="S22" t="n">
-        <v>-0.3523</v>
-      </c>
-      <c r="T22" t="n">
-        <v>-0.1415</v>
-      </c>
-      <c r="U22" t="n">
-        <v>-0.2109</v>
-      </c>
-      <c r="V22" t="n">
-        <v>-1.0722</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0805</v>
+        <v>-0.9748</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4973</v>
+        <v>-0.2511</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4168</v>
+        <v>-0.7237</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5304</v>
+        <v>-0.5532</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6951</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1647</v>
+        <v>-0.4885</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6875</v>
+        <v>-0.5815</v>
       </c>
       <c r="K23" t="n">
-        <v>1.163</v>
+        <v>0.168</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4756</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1571</v>
+        <v>0.0283</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5321</v>
+        <v>-0.2327</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6891</v>
+        <v>0.261</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.7112</v>
+        <v>0.4639</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.7988</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5802</v>
+        <v>0.1867</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6721</v>
+        <v>0.3304</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.908</v>
+        <v>-0.1436</v>
       </c>
       <c r="V23" t="n">
-        <v>2.6805</v>
+        <v>-1.0722</v>
       </c>
       <c r="W23" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.806</v>
+        <v>-1.5986</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8993</v>
+        <v>-3.0737</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0934</v>
+        <v>1.4751</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6673</v>
@@ -2326,13 +2326,13 @@
         <v>2.3195</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2109</v>
+        <v>0.9966</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1924</v>
+        <v>0.6332</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0184</v>
+        <v>0.3633</v>
       </c>
       <c r="V24" t="n">
         <v>1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.165</v>
+        <v>-3.8397</v>
       </c>
       <c r="E25" t="n">
         <v>-1.3515</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8134</v>
+        <v>-2.4881</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1973</v>
@@ -2404,13 +2404,13 @@
         <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1199</v>
+        <v>0.4452</v>
       </c>
       <c r="T25" t="n">
         <v>0.5034</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3835</v>
+        <v>-0.0582</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>10.424</v>
+        <v>12.783</v>
       </c>
       <c r="E26" t="n">
-        <v>4.086600000000002</v>
+        <v>4.0867</v>
       </c>
       <c r="F26" t="n">
-        <v>6.3375</v>
+        <v>8.696599999999997</v>
       </c>
       <c r="G26" t="n">
-        <v>6.919299999999998</v>
+        <v>6.919300000000002</v>
       </c>
       <c r="H26" t="n">
         <v>15.3179</v>
@@ -2482,16 +2482,16 @@
         <v>18.5562</v>
       </c>
       <c r="S26" t="n">
-        <v>4.893800000000001</v>
+        <v>7.2528</v>
       </c>
       <c r="T26" t="n">
-        <v>5.5264</v>
+        <v>5.5263</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6326000000000001</v>
+        <v>1.7266</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9303999999999997</v>
+        <v>0.9303999999999999</v>
       </c>
       <c r="W26" t="n">
         <v>9.175899999999999</v>
